--- a/reports/Debug-purgatory-20260111/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260111/For The Week Ending (Actual)_Visits.xlsx
@@ -521,10 +521,10 @@
         <v>46027</v>
       </c>
       <c r="C8" s="2">
-        <v>565</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +532,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>568</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C10" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -560,13 +560,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C11" s="2">
-        <v>667</v>
+        <v>1128</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -577,10 +577,10 @@
         <v>46030</v>
       </c>
       <c r="C12" s="2">
-        <v>976</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>1354</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -605,10 +605,10 @@
         <v>46032</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>849</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C15" s="2">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46033</v>
+        <v>46027</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -644,13 +644,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46033</v>
+        <v>46027</v>
       </c>
       <c r="C17" s="2">
-        <v>533</v>
+        <v>322</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,10 +658,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>46033</v>
+        <v>46028</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="C19" s="2">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="C20" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -703,10 +703,10 @@
         <v>46029</v>
       </c>
       <c r="C21" s="2">
-        <v>183</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -731,10 +731,10 @@
         <v>46030</v>
       </c>
       <c r="C23" s="2">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +742,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C24" s="2">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -756,13 +756,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C25" s="2">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C26" s="2">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46033</v>
+        <v>46027</v>
       </c>
       <c r="C27" s="2">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -801,10 +801,10 @@
         <v>46027</v>
       </c>
       <c r="C28" s="2">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -815,7 +815,7 @@
         <v>46028</v>
       </c>
       <c r="C29" s="2">
-        <v>568</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -829,10 +829,10 @@
         <v>46028</v>
       </c>
       <c r="C30" s="2">
-        <v>59</v>
+        <v>1411</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -843,10 +843,10 @@
         <v>46029</v>
       </c>
       <c r="C31" s="2">
-        <v>1128</v>
+        <v>460</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -857,10 +857,10 @@
         <v>46030</v>
       </c>
       <c r="C32" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -871,7 +871,7 @@
         <v>46031</v>
       </c>
       <c r="C33" s="2">
-        <v>1354</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C34" s="2">
-        <v>849</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46033</v>
+        <v>46031</v>
       </c>
       <c r="C35" s="2">
-        <v>14</v>
+        <v>837</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="C36" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="C37" s="2">
-        <v>322</v>
+        <v>49</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46028</v>
+        <v>46032</v>
       </c>
       <c r="C38" s="2">
-        <v>97</v>
+        <v>2029</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,10 +952,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,10 +966,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="C40" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C41" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -997,7 +997,7 @@
         <v>46030</v>
       </c>
       <c r="C42" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1011,10 +1011,10 @@
         <v>46030</v>
       </c>
       <c r="C43" s="2">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1025,7 +1025,7 @@
         <v>46031</v>
       </c>
       <c r="C44" s="2">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,13 +1036,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46033</v>
+        <v>46031</v>
       </c>
       <c r="C45" s="2">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C46" s="2">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46027</v>
+        <v>46033</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,13 +1078,13 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46027</v>
+        <v>46033</v>
       </c>
       <c r="C48" s="2">
-        <v>1403</v>
+        <v>18</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46027</v>
+        <v>46033</v>
       </c>
       <c r="C49" s="2">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46028</v>
+        <v>46033</v>
       </c>
       <c r="C50" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C51" s="2">
-        <v>2</v>
+        <v>565</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1137,7 +1137,7 @@
         <v>46029</v>
       </c>
       <c r="C52" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C53" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C54" s="2">
-        <v>8</v>
+        <v>667</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,13 +1176,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>976</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,7 +1193,7 @@
         <v>46032</v>
       </c>
       <c r="C56" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1207,7 +1207,7 @@
         <v>46032</v>
       </c>
       <c r="C57" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C58" s="2">
-        <v>1375</v>
+        <v>44</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1235,7 +1235,7 @@
         <v>46033</v>
       </c>
       <c r="C59" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,13 +1246,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>46027</v>
+        <v>46033</v>
       </c>
       <c r="C60" s="2">
-        <v>2</v>
+        <v>533</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>46027</v>
+        <v>46033</v>
       </c>
       <c r="C61" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C62" s="2">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1291,10 +1291,10 @@
         <v>46028</v>
       </c>
       <c r="C63" s="2">
-        <v>1411</v>
+        <v>4</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1305,10 +1305,10 @@
         <v>46029</v>
       </c>
       <c r="C64" s="2">
-        <v>460</v>
+        <v>183</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C65" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C66" s="2">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C67" s="2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1358,13 +1358,13 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C68" s="2">
-        <v>837</v>
+        <v>130</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C69" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>46031</v>
+        <v>46033</v>
       </c>
       <c r="C70" s="2">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>46032</v>
+        <v>46027</v>
       </c>
       <c r="C71" s="2">
-        <v>2029</v>
+        <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>5</v>
@@ -1417,10 +1417,10 @@
         <v>46027</v>
       </c>
       <c r="C72" s="2">
-        <v>12</v>
+        <v>1403</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1431,7 +1431,7 @@
         <v>46027</v>
       </c>
       <c r="C73" s="2">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1445,7 +1445,7 @@
         <v>46028</v>
       </c>
       <c r="C74" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="C75" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>5</v>
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C76" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C77" s="2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1501,10 +1501,10 @@
         <v>46031</v>
       </c>
       <c r="C78" s="2">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C79" s="2">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C80" s="2">
         <v>4</v>
@@ -1540,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C81" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
@@ -1557,7 +1557,7 @@
         <v>46033</v>
       </c>
       <c r="C82" s="2">
-        <v>7</v>
+        <v>1375</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>5</v>
@@ -1571,7 +1571,7 @@
         <v>46033</v>
       </c>
       <c r="C83" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
